--- a/plantilla_notas_tablero_docente.xlsx
+++ b/plantilla_notas_tablero_docente.xlsx
@@ -1,46 +1,159 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OMAR\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A411780C-E0EB-44B3-B834-023B58E0BE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
     <sheet name="Curso" sheetId="2" r:id="rId2"/>
     <sheet name="Notas" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
+  <si>
+    <t>PLANTILLA PARA CARGAR NOTAS – Tablero Docente</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Úsala solo si no tienes el acta parcial en PDF de UNIPAZ (si la tienes, súbela directamente).</t>
+  </si>
+  <si>
+    <t>1. En la hoja "Curso" escribe los datos de tu asignatura, los pesos de cada corte (deben sumar 100) y la intensidad horaria total.</t>
+  </si>
+  <si>
+    <t>2. En la hoja "Notas" escribe un estudiante por fila. Borra las 3 filas de ejemplo (las que empiezan por "EJEMPLO").</t>
+  </si>
+  <si>
+    <t>3. Notas con decimales de 0 a 5 (coma o punto). Si un corte aún no se ha calificado, deja la nota VACÍA (no escribas 0).</t>
+  </si>
+  <si>
+    <t>4. Faltas: número de horas o clases perdidas en ese corte. Si no hubo, deja vacío o pon 0.</t>
+  </si>
+  <si>
+    <t>5. No cambies los nombres de las columnas. Si tu asignatura tiene solo 2 cortes, borra las columnas del 3er Corte y ajusta los pesos.</t>
+  </si>
+  <si>
+    <t>6. Guarda el archivo y arrástralo a la herramienta.</t>
+  </si>
+  <si>
+    <t>Nota: puedes poner varias asignaturas en la misma hoja añadiendo las columnas opcionales Asignatura, Grupo y Periodo.</t>
+  </si>
+  <si>
+    <t>Dato</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Asignatura</t>
+  </si>
+  <si>
+    <t>NOMBRE DE LA ASIGNATURA</t>
+  </si>
+  <si>
+    <t>Código</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Periodo</t>
+  </si>
+  <si>
+    <t>2026-2S</t>
+  </si>
+  <si>
+    <t>Peso 1er Corte (%)</t>
+  </si>
+  <si>
+    <t>Peso 2do Corte (%)</t>
+  </si>
+  <si>
+    <t>Peso 3er Corte (%)</t>
+  </si>
+  <si>
+    <t>Intensidad horaria total (horas)</t>
+  </si>
+  <si>
+    <t>Documento</t>
+  </si>
+  <si>
+    <t>Estudiante</t>
+  </si>
+  <si>
+    <t>1er Corte (nota)</t>
+  </si>
+  <si>
+    <t>1er Corte (faltas)</t>
+  </si>
+  <si>
+    <t>2do Corte (nota)</t>
+  </si>
+  <si>
+    <t>2do Corte (faltas)</t>
+  </si>
+  <si>
+    <t>3er Corte (nota)</t>
+  </si>
+  <si>
+    <t>3er Corte (faltas)</t>
+  </si>
+  <si>
+    <t>1000000001</t>
+  </si>
+  <si>
+    <t>EJEMPLO PEREZ, ANA</t>
+  </si>
+  <si>
+    <t>1000000002</t>
+  </si>
+  <si>
+    <t>EJEMPLO ROJAS, CARLOS</t>
+  </si>
+  <si>
+    <t>1000000003</t>
+  </si>
+  <si>
+    <t>EJEMPLO LUNA, DIANA</t>
+  </si>
+  <si>
+    <t>codigo asignatura (opcional)</t>
+  </si>
+  <si>
+    <t>DIURNO (D1, D2) / NOCTURNO (N1, N2)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -66,14 +179,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -398,212 +520,212 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="120.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>PLANTILLA PARA CARGAR NOTAS – Tablero Docente</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Úsala solo si no tienes el acta parcial en PDF de UNIPAZ (si la tienes, súbela directamente).</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>1. En la hoja "Curso" escribe los datos de tu asignatura, los pesos de cada corte (deben sumar 100) y la intensidad horaria total.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>2. En la hoja "Notas" escribe un estudiante por fila. Borra las 3 filas de ejemplo (las que empiezan por "EJEMPLO").</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>3. Notas con decimales de 0 a 5 (coma o punto). Si un corte aún no se ha calificado, deja la nota VACÍA (no escribas 0).</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>4. Faltas: número de horas o clases perdidas en ese corte. Si no hubo, deja vacío o pon 0.</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>5. No cambies los nombres de las columnas. Si tu asignatura tiene solo 2 cortes, borra las columnas del 3er Corte y ajusta los pesos.</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>6. Guarda el archivo y arrástralo a la herramienta.</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Nota: puedes poner varias asignaturas en la misma hoja añadiendo las columnas opcionales Asignatura, Grupo y Periodo.</v>
+    <row r="1" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A12"/>
+    <ignoredError sqref="A1:A12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36.83203125" customWidth="1"/>
-    <col min="2" max="2" width="36.83203125" customWidth="1"/>
+    <col min="1" max="1" width="27.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Dato</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Valor</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Asignatura</v>
-      </c>
-      <c r="B2" t="str">
-        <v>NOMBRE DE LA ASIGNATURA</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Código</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Grupo</v>
-      </c>
-      <c r="B4" t="str">
-        <v>GRUPO DIURNO</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Periodo</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-2S</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Peso 1er Corte (%)</v>
+    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B6">
         <v>30</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Peso 2do Corte (%)</v>
+    <row r="7" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="B7">
         <v>30</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Peso 3er Corte (%)</v>
+    <row r="8" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="B8">
         <v>40</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Intensidad horaria total (horas)</v>
+    <row r="9" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="B9">
         <v>48</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
+    <ignoredError sqref="A1:B2 A5:B9 A3 A4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="36.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="3" max="8" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Documento</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Estudiante</v>
-      </c>
-      <c r="C1" t="str">
-        <v>1er Corte (nota)</v>
-      </c>
-      <c r="D1" t="str">
-        <v>1er Corte (faltas)</v>
-      </c>
-      <c r="E1" t="str">
-        <v>2do Corte (nota)</v>
-      </c>
-      <c r="F1" t="str">
-        <v>2do Corte (faltas)</v>
-      </c>
-      <c r="G1" t="str">
-        <v>3er Corte (nota)</v>
-      </c>
-      <c r="H1" t="str">
-        <v>3er Corte (faltas)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1000000001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>EJEMPLO PEREZ, ANA</v>
+    <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
       </c>
       <c r="C2">
         <v>4.2</v>
@@ -618,12 +740,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>1000000002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>EJEMPLO ROJAS, CARLOS</v>
+    <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
       </c>
       <c r="C3">
         <v>2.9</v>
@@ -638,12 +760,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>1000000003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>EJEMPLO LUNA, DIANA</v>
+    <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
       </c>
       <c r="C4">
         <v>3.5</v>
@@ -658,9 +780,11 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35"/>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
+    <ignoredError sqref="A1:H4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/plantilla_notas_tablero_docente.xlsx
+++ b/plantilla_notas_tablero_docente.xlsx
@@ -1,159 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OMAR\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A411780C-E0EB-44B3-B834-023B58E0BE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
     <sheet name="Curso" sheetId="2" r:id="rId2"/>
     <sheet name="Notas" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
-  <si>
-    <t>PLANTILLA PARA CARGAR NOTAS – Tablero Docente</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Úsala solo si no tienes el acta parcial en PDF de UNIPAZ (si la tienes, súbela directamente).</t>
-  </si>
-  <si>
-    <t>1. En la hoja "Curso" escribe los datos de tu asignatura, los pesos de cada corte (deben sumar 100) y la intensidad horaria total.</t>
-  </si>
-  <si>
-    <t>2. En la hoja "Notas" escribe un estudiante por fila. Borra las 3 filas de ejemplo (las que empiezan por "EJEMPLO").</t>
-  </si>
-  <si>
-    <t>3. Notas con decimales de 0 a 5 (coma o punto). Si un corte aún no se ha calificado, deja la nota VACÍA (no escribas 0).</t>
-  </si>
-  <si>
-    <t>4. Faltas: número de horas o clases perdidas en ese corte. Si no hubo, deja vacío o pon 0.</t>
-  </si>
-  <si>
-    <t>5. No cambies los nombres de las columnas. Si tu asignatura tiene solo 2 cortes, borra las columnas del 3er Corte y ajusta los pesos.</t>
-  </si>
-  <si>
-    <t>6. Guarda el archivo y arrástralo a la herramienta.</t>
-  </si>
-  <si>
-    <t>Nota: puedes poner varias asignaturas en la misma hoja añadiendo las columnas opcionales Asignatura, Grupo y Periodo.</t>
-  </si>
-  <si>
-    <t>Dato</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Asignatura</t>
-  </si>
-  <si>
-    <t>NOMBRE DE LA ASIGNATURA</t>
-  </si>
-  <si>
-    <t>Código</t>
-  </si>
-  <si>
-    <t>Grupo</t>
-  </si>
-  <si>
-    <t>Periodo</t>
-  </si>
-  <si>
-    <t>2026-2S</t>
-  </si>
-  <si>
-    <t>Peso 1er Corte (%)</t>
-  </si>
-  <si>
-    <t>Peso 2do Corte (%)</t>
-  </si>
-  <si>
-    <t>Peso 3er Corte (%)</t>
-  </si>
-  <si>
-    <t>Intensidad horaria total (horas)</t>
-  </si>
-  <si>
-    <t>Documento</t>
-  </si>
-  <si>
-    <t>Estudiante</t>
-  </si>
-  <si>
-    <t>1er Corte (nota)</t>
-  </si>
-  <si>
-    <t>1er Corte (faltas)</t>
-  </si>
-  <si>
-    <t>2do Corte (nota)</t>
-  </si>
-  <si>
-    <t>2do Corte (faltas)</t>
-  </si>
-  <si>
-    <t>3er Corte (nota)</t>
-  </si>
-  <si>
-    <t>3er Corte (faltas)</t>
-  </si>
-  <si>
-    <t>1000000001</t>
-  </si>
-  <si>
-    <t>EJEMPLO PEREZ, ANA</t>
-  </si>
-  <si>
-    <t>1000000002</t>
-  </si>
-  <si>
-    <t>EJEMPLO ROJAS, CARLOS</t>
-  </si>
-  <si>
-    <t>1000000003</t>
-  </si>
-  <si>
-    <t>EJEMPLO LUNA, DIANA</t>
-  </si>
-  <si>
-    <t>codigo asignatura (opcional)</t>
-  </si>
-  <si>
-    <t>DIURNO (D1, D2) / NOCTURNO (N1, N2)</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -179,23 +66,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -520,212 +398,212 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="120.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>9</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>PLANTILLA PARA CARGAR NOTAS – Tablero Docente</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Úsala solo si no tienes el acta parcial en PDF de UNIPAZ (si la tienes, súbela directamente).</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>1. En la hoja "Curso" escribe los datos de tu asignatura, los pesos de cada corte (deben sumar 100) y la intensidad horaria total.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2. En la hoja "Notas" escribe un estudiante por fila. Borra las 3 filas de ejemplo (las que empiezan por "EJEMPLO").</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>3. Notas con decimales de 0 a 5 (coma o punto). Si un corte aún no se ha calificado, deja la nota VACÍA (no escribas 0).</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>4. Faltas: número de horas o clases perdidas en ese corte. Si no hubo, deja vacío o pon 0.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>5. No cambies los nombres de las columnas. Si tu asignatura tiene solo 2 cortes, borra las columnas del 3er Corte y ajusta los pesos.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>6. Guarda el archivo y arrástralo a la herramienta.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Nota: puedes poner varias asignaturas en la misma hoja añadiendo las columnas opcionales Asignatura, Grupo y Periodo.</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:A12" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.08203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.83203125" customWidth="1"/>
+    <col min="2" max="2" width="36.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Dato</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Valor</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Asignatura</v>
+      </c>
+      <c r="B2" t="str">
+        <v>NOMBRE DE LA ASIGNATURA</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Código</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Grupo</v>
+      </c>
+      <c r="B4" t="str">
+        <v>GRUPO DIURNO</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Periodo</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-2S</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Peso 1er Corte (%)</v>
       </c>
       <c r="B6">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Peso 2do Corte (%)</v>
       </c>
       <c r="B7">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>20</v>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Peso 3er Corte (%)</v>
       </c>
       <c r="B8">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Intensidad horaria total (horas)</v>
       </c>
       <c r="B9">
         <v>48</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B2 A5:B9 A3 A4" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H4"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="36.83203125" customWidth="1"/>
-    <col min="3" max="8" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>31</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Documento</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Estudiante</v>
+      </c>
+      <c r="C1" t="str">
+        <v>1er Corte (nota)</v>
+      </c>
+      <c r="D1" t="str">
+        <v>1er Corte (faltas)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>2do Corte (nota)</v>
+      </c>
+      <c r="F1" t="str">
+        <v>2do Corte (faltas)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>3er Corte (nota)</v>
+      </c>
+      <c r="H1" t="str">
+        <v>3er Corte (faltas)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1000000001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>EJEMPLO PEREZ, ANA</v>
       </c>
       <c r="C2">
         <v>4.2</v>
@@ -740,12 +618,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" t="s">
-        <v>33</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>1000000002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>EJEMPLO ROJAS, CARLOS</v>
       </c>
       <c r="C3">
         <v>2.9</v>
@@ -760,12 +638,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>35</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>1000000003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>EJEMPLO LUNA, DIANA</v>
       </c>
       <c r="C4">
         <v>3.5</v>
@@ -780,11 +658,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H4" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>